--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827869415283</t>
+    <t xml:space="preserve">8.66827964782715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -131,64 +131,64 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178949356079</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29213,7 +29213,7 @@
     </row>
     <row r="1078">
       <c r="A1078" s="1" t="n">
-        <v>45940.6443287037</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1078" t="n">
         <v>1402</v>
@@ -29234,6 +29234,32 @@
         <v>286</v>
       </c>
       <c r="H1078" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>45943.6494212963</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>273</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>35.5999984741211</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>35.4000015258789</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>35.4000015258789</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>35.5999984741211</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1079" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860996246338</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827964782715</t>
+    <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
     <t xml:space="preserve">8.6331844329834</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -152,43 +152,43 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,25 +200,25 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178949356079</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669523239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282726287842</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
@@ -236,34 +236,34 @@
     <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29239,7 +29239,7 @@
     </row>
     <row r="1079">
       <c r="A1079" s="1" t="n">
-        <v>45943.6494212963</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1079" t="n">
         <v>273</v>
@@ -29260,6 +29260,32 @@
         <v>286</v>
       </c>
       <c r="H1079" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>45944.6440046296</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>2132</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>35.5999984741211</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>285</v>
+      </c>
+      <c r="H1080" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035308837891</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516376495361</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223831176758</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844064712524</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669523239136</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282726287842</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -874,6 +874,9 @@
   <si>
     <t xml:space="preserve">35.5999984741211</t>
   </si>
+  <si>
+    <t xml:space="preserve">35.7000007629395</t>
+  </si>
 </sst>
 </file>
 
@@ -29265,7 +29268,7 @@
     </row>
     <row r="1080">
       <c r="A1080" s="1" t="n">
-        <v>45944.6440046296</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1080" t="n">
         <v>2132</v>
@@ -29286,6 +29289,32 @@
         <v>285</v>
       </c>
       <c r="H1080" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>45945.6494560185</v>
+      </c>
+      <c r="B1081" t="n">
+        <v>10885</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>287</v>
+      </c>
+      <c r="H1081" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -131,70 +131,70 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,25 +221,25 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t xml:space="preserve">35.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7999992370605</t>
   </si>
 </sst>
 </file>
@@ -29294,7 +29297,7 @@
     </row>
     <row r="1081">
       <c r="A1081" s="1" t="n">
-        <v>45945.6494560185</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1081" t="n">
         <v>10885</v>
@@ -29315,6 +29318,32 @@
         <v>287</v>
       </c>
       <c r="H1081" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>45946.649537037</v>
+      </c>
+      <c r="B1082" t="n">
+        <v>1957</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1082" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073013305664</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969436645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478862762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091705322266</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -155,16 +155,16 @@
     <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025737762451</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157768249512</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.3966693878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773309707642</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
     <t xml:space="preserve">11.6635065078735</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445806503296</t>
@@ -29323,7 +29323,7 @@
     </row>
     <row r="1082">
       <c r="A1082" s="1" t="n">
-        <v>45946.649537037</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1082" t="n">
         <v>1957</v>
@@ -29344,6 +29344,32 @@
         <v>288</v>
       </c>
       <c r="H1082" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>45947.6431597222</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>942</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1083" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -29349,7 +29349,7 @@
     </row>
     <row r="1083">
       <c r="A1083" s="1" t="n">
-        <v>45947.6431597222</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B1083" t="n">
         <v>942</v>
@@ -29370,6 +29370,32 @@
         <v>288</v>
       </c>
       <c r="H1083" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>45950.6494097222</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>46</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="G1084" t="s">
+        <v>287</v>
+      </c>
+      <c r="H1084" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969436645508</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478862762451</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.0018606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157768249512</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353490829468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282745361328</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966693878174</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773309707642</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29375,7 +29375,7 @@
     </row>
     <row r="1084">
       <c r="A1084" s="1" t="n">
-        <v>45950.6494097222</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1084" t="n">
         <v>46</v>
@@ -29396,6 +29396,32 @@
         <v>287</v>
       </c>
       <c r="H1084" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>45951.6425462963</v>
+      </c>
+      <c r="B1085" t="n">
+        <v>261</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1085" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1085" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035499572754</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -158,55 +158,55 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018606185913</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025737762451</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353490829468</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282745361328</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445816040039</t>
@@ -880,6 +880,9 @@
   <si>
     <t xml:space="preserve">35.7999992370605</t>
   </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
 </sst>
 </file>
 
@@ -29401,7 +29404,7 @@
     </row>
     <row r="1085">
       <c r="A1085" s="1" t="n">
-        <v>45951.6425462963</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1085" t="n">
         <v>261</v>
@@ -29422,6 +29425,32 @@
         <v>288</v>
       </c>
       <c r="H1085" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>45952.6510416667</v>
+      </c>
+      <c r="B1086" t="n">
+        <v>379412</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1086" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1086" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195728302002</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -101,31 +101,31 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.7384672164917</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844064712524</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353471755981</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
@@ -883,6 +883,9 @@
   <si>
     <t xml:space="preserve">36</t>
   </si>
+  <si>
+    <t xml:space="preserve">36.0999984741211</t>
+  </si>
 </sst>
 </file>
 
@@ -29430,7 +29433,7 @@
     </row>
     <row r="1086">
       <c r="A1086" s="1" t="n">
-        <v>45952.6510416667</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1086" t="n">
         <v>379412</v>
@@ -29451,6 +29454,32 @@
         <v>289</v>
       </c>
       <c r="H1086" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>45953.6494560185</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>6784</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1087" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035308837891</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860996246338</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195728302002</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
     <t xml:space="preserve">8.7384672164917</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157768249512</t>
@@ -176,25 +176,25 @@
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178939819336</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445816040039</t>
@@ -29459,7 +29459,7 @@
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>45953.6494560185</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1087" t="n">
         <v>6784</v>
@@ -29480,6 +29480,32 @@
         <v>290</v>
       </c>
       <c r="H1087" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>45954.6398263889</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>2804</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1088" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195728302002</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931571960449</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089332580566</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29485,7 +29485,7 @@
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>45954.6398263889</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B1088" t="n">
         <v>2804</v>
@@ -29506,6 +29506,32 @@
         <v>290</v>
       </c>
       <c r="H1088" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="1" t="n">
+        <v>45957.6911574074</v>
+      </c>
+      <c r="B1089" t="n">
+        <v>471</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1089" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1089" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895957946777</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157958984375</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546875</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740259170532</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669523239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282726287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179456710815</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924760818481</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29511,7 +29511,7 @@
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>45957.6911574074</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1089" t="n">
         <v>471</v>
@@ -29532,6 +29532,32 @@
         <v>289</v>
       </c>
       <c r="H1089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="1" t="n">
+        <v>45958.6912037037</v>
+      </c>
+      <c r="B1090" t="n">
+        <v>3057</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035308837891</t>
+    <t xml:space="preserve">8.51035499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
@@ -86,19 +86,19 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
     <t xml:space="preserve">8.99289989471436</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.7384672164917</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -152,37 +152,37 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862897872925</t>
@@ -218,28 +218,28 @@
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669523239136</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282726287842</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29537,7 +29537,7 @@
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>45958.6912037037</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1090" t="n">
         <v>3057</v>
@@ -29558,6 +29558,32 @@
         <v>289</v>
       </c>
       <c r="H1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="1" t="n">
+        <v>45959.6809143518</v>
+      </c>
+      <c r="B1091" t="n">
+        <v>4703</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1091" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035499572754</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422306060791</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
     <t xml:space="preserve">8.7384672164917</t>
@@ -137,25 +137,25 @@
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
@@ -221,25 +221,25 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29563,7 +29563,7 @@
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
-        <v>45959.6809143518</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1091" t="n">
         <v>4703</v>
@@ -29584,6 +29584,32 @@
         <v>290</v>
       </c>
       <c r="H1091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
+        <v>45960.6912731481</v>
+      </c>
+      <c r="B1092" t="n">
+        <v>13446</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1092" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -62,13 +62,13 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -101,34 +101,34 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
@@ -137,73 +137,73 @@
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
@@ -212,46 +212,46 @@
     <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445816040039</t>
@@ -29589,13 +29589,13 @@
     </row>
     <row r="1092">
       <c r="A1092" s="1" t="n">
-        <v>45960.6912731481</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1092" t="n">
         <v>13446</v>
       </c>
       <c r="C1092" t="n">
-        <v>36</v>
+        <v>36.0999984741211</v>
       </c>
       <c r="D1092" t="n">
         <v>36</v>
@@ -29610,6 +29610,32 @@
         <v>290</v>
       </c>
       <c r="H1092" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="1" t="n">
+        <v>45961.6911342593</v>
+      </c>
+      <c r="B1093" t="n">
+        <v>179</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1093" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -104,25 +104,25 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792152404785</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178939819336</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089332580566</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773309707642</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29615,7 +29615,7 @@
     </row>
     <row r="1093">
       <c r="A1093" s="1" t="n">
-        <v>45961.6911342593</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1093" t="n">
         <v>179</v>
@@ -29636,6 +29636,32 @@
         <v>290</v>
       </c>
       <c r="H1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>45964.6314467593</v>
+      </c>
+      <c r="B1094" t="n">
+        <v>3512</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860996246338</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.7386531829834</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178939819336</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29641,7 +29641,7 @@
     </row>
     <row r="1094">
       <c r="A1094" s="1" t="n">
-        <v>45964.6314467593</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1094" t="n">
         <v>3512</v>
@@ -29662,6 +29662,32 @@
         <v>289</v>
       </c>
       <c r="H1094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="1" t="n">
+        <v>45965.6867824074</v>
+      </c>
+      <c r="B1095" t="n">
+        <v>114</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1095" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
@@ -167,43 +167,43 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931571960449</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
@@ -212,31 +212,31 @@
     <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089332580566</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445816040039</t>
@@ -29667,7 +29667,7 @@
     </row>
     <row r="1095">
       <c r="A1095" s="1" t="n">
-        <v>45965.6867824074</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1095" t="n">
         <v>114</v>
@@ -29688,6 +29688,32 @@
         <v>289</v>
       </c>
       <c r="H1095" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>45966.6910300926</v>
+      </c>
+      <c r="B1096" t="n">
+        <v>580</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1096" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.7386531829834</t>
@@ -146,43 +146,43 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
@@ -239,25 +239,25 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -266,25 +266,25 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924760818481</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079010009766</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29693,10 +29693,10 @@
     </row>
     <row r="1096">
       <c r="A1096" s="1" t="n">
-        <v>45966.6910300926</v>
+        <v>45967.6858680556</v>
       </c>
       <c r="B1096" t="n">
-        <v>580</v>
+        <v>3669</v>
       </c>
       <c r="C1096" t="n">
         <v>36</v>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860996246338</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -95,43 +95,43 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.0018606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157768249512</t>
@@ -173,22 +173,22 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353490829468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282745361328</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29693,10 +29693,10 @@
     </row>
     <row r="1096">
       <c r="A1096" s="1" t="n">
-        <v>45967.6858680556</v>
+        <v>45968.6477199074</v>
       </c>
       <c r="B1096" t="n">
-        <v>3669</v>
+        <v>2945</v>
       </c>
       <c r="C1096" t="n">
         <v>36</v>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035499572754</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018606185913</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025737762451</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157768249512</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931571960449</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353490829468</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -227,31 +227,31 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282745361328</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
     <t xml:space="preserve">12.7113990783691</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
     <t xml:space="preserve">12.2102327346802</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -29693,10 +29693,10 @@
     </row>
     <row r="1096">
       <c r="A1096" s="1" t="n">
-        <v>45968.6477199074</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B1096" t="n">
-        <v>2945</v>
+        <v>580</v>
       </c>
       <c r="C1096" t="n">
         <v>36</v>
@@ -29714,6 +29714,84 @@
         <v>289</v>
       </c>
       <c r="H1096" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1097" t="n">
+        <v>3669</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1097" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1098" t="n">
+        <v>2945</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1098" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="1" t="n">
+        <v>45971.6681018519</v>
+      </c>
+      <c r="B1099" t="n">
+        <v>3748</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1099" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356052398682</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931571960449</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301578521729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089332580566</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
@@ -29771,7 +29771,7 @@
     </row>
     <row r="1099">
       <c r="A1099" s="1" t="n">
-        <v>45971.6681018519</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B1099" t="n">
         <v>3748</v>
@@ -29792,6 +29792,32 @@
         <v>289</v>
       </c>
       <c r="H1099" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="1" t="n">
+        <v>45972.6301273148</v>
+      </c>
+      <c r="B1100" t="n">
+        <v>1946</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1100" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -53,28 +53,28 @@
     <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582439422607</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -83,28 +83,28 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895957946777</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018577575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792161941528</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740249633789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301578521729</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29797,7 +29797,7 @@
     </row>
     <row r="1100">
       <c r="A1100" s="1" t="n">
-        <v>45972.6301273148</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1100" t="n">
         <v>1946</v>
@@ -29818,6 +29818,32 @@
         <v>290</v>
       </c>
       <c r="H1100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="1" t="n">
+        <v>45973.691099537</v>
+      </c>
+      <c r="B1101" t="n">
+        <v>9437</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1101" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091609954834</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018577575684</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -173,46 +173,46 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740249633789</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29823,7 +29823,7 @@
     </row>
     <row r="1101">
       <c r="A1101" s="1" t="n">
-        <v>45973.691099537</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B1101" t="n">
         <v>9437</v>
@@ -29844,6 +29844,32 @@
         <v>289</v>
       </c>
       <c r="H1101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="1" t="n">
+        <v>45974.6910300926</v>
+      </c>
+      <c r="B1102" t="n">
+        <v>563</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1102" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,31 +62,31 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827869415283</t>
+    <t xml:space="preserve">8.66827964782715</t>
   </si>
   <si>
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5631799697876</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931476593018</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844045639038</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792152404785</t>
@@ -206,22 +206,22 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178949356079</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -248,37 +248,37 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
     <t xml:space="preserve">11.6635065078735</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924751281738</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29849,7 +29849,7 @@
     </row>
     <row r="1102">
       <c r="A1102" s="1" t="n">
-        <v>45974.6910300926</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B1102" t="n">
         <v>563</v>
@@ -29870,6 +29870,32 @@
         <v>290</v>
       </c>
       <c r="H1102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="1" t="n">
+        <v>45975.6910069444</v>
+      </c>
+      <c r="B1103" t="n">
+        <v>385</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1103" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -53,13 +53,13 @@
     <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827964782715</t>
+    <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091705322266</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.0018587112427</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178949356079</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
     <t xml:space="preserve">11.6635065078735</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445806503296</t>
@@ -29875,7 +29875,7 @@
     </row>
     <row r="1103">
       <c r="A1103" s="1" t="n">
-        <v>45975.6910069444</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1103" t="n">
         <v>385</v>
@@ -29896,6 +29896,32 @@
         <v>289</v>
       </c>
       <c r="H1103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="1" t="n">
+        <v>45978.6857986111</v>
+      </c>
+      <c r="B1104" t="n">
+        <v>30237</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1104" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860996246338</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.0018577575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740249633789</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178939819336</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985536575317</t>
@@ -886,6 +886,9 @@
   <si>
     <t xml:space="preserve">36.0999984741211</t>
   </si>
+  <si>
+    <t xml:space="preserve">35.9000015258789</t>
+  </si>
 </sst>
 </file>
 
@@ -29901,7 +29904,7 @@
     </row>
     <row r="1104">
       <c r="A1104" s="1" t="n">
-        <v>45978.6857986111</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B1104" t="n">
         <v>30237</v>
@@ -29922,6 +29925,32 @@
         <v>289</v>
       </c>
       <c r="H1104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="1" t="n">
+        <v>45979.6832291667</v>
+      </c>
+      <c r="B1105" t="n">
+        <v>328172</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1105" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931541442871</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478862762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.81742858886719</t>
@@ -101,46 +101,46 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091609954834</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895957946777</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018577575684</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792161941528</t>
@@ -209,28 +209,28 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740249633789</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669523239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
     <t xml:space="preserve">10.3089351654053</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985536575317</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445806503296</t>
@@ -29930,7 +29930,7 @@
     </row>
     <row r="1105">
       <c r="A1105" s="1" t="n">
-        <v>45979.6832291667</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B1105" t="n">
         <v>328172</v>
@@ -29951,6 +29951,32 @@
         <v>291</v>
       </c>
       <c r="H1105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="1" t="n">
+        <v>45980.6910763889</v>
+      </c>
+      <c r="B1106" t="n">
+        <v>327</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1106" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
@@ -77,37 +77,37 @@
     <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478862762451</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997444152832</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -131,31 +131,31 @@
     <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -164,49 +164,49 @@
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476110458374</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669523239136</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -230,43 +230,43 @@
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,28 +305,28 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -29956,7 +29956,7 @@
     </row>
     <row r="1106">
       <c r="A1106" s="1" t="n">
-        <v>45980.6910763889</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B1106" t="n">
         <v>327</v>
@@ -29977,6 +29977,32 @@
         <v>288</v>
       </c>
       <c r="H1106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="1" t="n">
+        <v>45981.6865740741</v>
+      </c>
+      <c r="B1107" t="n">
+        <v>2902</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.76478672027588</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
@@ -119,43 +119,43 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5631799697876</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -167,46 +167,46 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844045639038</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445816040039</t>
@@ -29982,7 +29982,7 @@
     </row>
     <row r="1107">
       <c r="A1107" s="1" t="n">
-        <v>45981.6865740741</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1107" t="n">
         <v>2902</v>
@@ -30003,6 +30003,32 @@
         <v>288</v>
       </c>
       <c r="H1107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="1" t="n">
+        <v>45982.6913078704</v>
+      </c>
+      <c r="B1108" t="n">
+        <v>87</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1108" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1108" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516376495361</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223831176758</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844064712524</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669523239136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282726287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -30008,7 +30008,7 @@
     </row>
     <row r="1108">
       <c r="A1108" s="1" t="n">
-        <v>45982.6913078704</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1108" t="n">
         <v>87</v>
@@ -30029,6 +30029,32 @@
         <v>288</v>
       </c>
       <c r="H1108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="1" t="n">
+        <v>45985.6911921296</v>
+      </c>
+      <c r="B1109" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1109" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035308837891</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.55422210693359</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,40 +62,40 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827869415283</t>
+    <t xml:space="preserve">8.66827964782715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318538665771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.0457277297974</t>
@@ -164,31 +164,31 @@
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862897872925</t>
@@ -212,43 +212,43 @@
     <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669523239136</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282726287842</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966693878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30034,13 +30034,13 @@
     </row>
     <row r="1109">
       <c r="A1109" s="1" t="n">
-        <v>45985.6911921296</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1109" t="n">
         <v>139</v>
       </c>
       <c r="C1109" t="n">
-        <v>35.7999992370605</v>
+        <v>36</v>
       </c>
       <c r="D1109" t="n">
         <v>35.7999992370605</v>
@@ -30055,6 +30055,32 @@
         <v>289</v>
       </c>
       <c r="H1109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="1" t="n">
+        <v>45986.6841435185</v>
+      </c>
+      <c r="B1110" t="n">
+        <v>1965</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1110" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1110" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195728302002</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827964782715</t>
+    <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318538665771</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -116,49 +116,49 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5631799697876</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
@@ -167,31 +167,31 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844045639038</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546875</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966693878174</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
     <t xml:space="preserve">11.7090663909912</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
@@ -30060,7 +30060,7 @@
     </row>
     <row r="1110">
       <c r="A1110" s="1" t="n">
-        <v>45986.6841435185</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1110" t="n">
         <v>1965</v>
@@ -30081,6 +30081,32 @@
         <v>288</v>
       </c>
       <c r="H1110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="1" t="n">
+        <v>45987.6912268518</v>
+      </c>
+      <c r="B1111" t="n">
+        <v>156</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1111" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860805511475</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157958984375</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282726287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30086,7 +30086,7 @@
     </row>
     <row r="1111">
       <c r="A1111" s="1" t="n">
-        <v>45987.6912268518</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B1111" t="n">
         <v>156</v>
@@ -30107,6 +30107,32 @@
         <v>288</v>
       </c>
       <c r="H1111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="1" t="n">
+        <v>45988.6578587963</v>
+      </c>
+      <c r="B1112" t="n">
+        <v>10463</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>35.7999992370605</v>
+      </c>
+      <c r="G1112" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1112" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582439422607</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356052398682</t>
@@ -80,46 +80,46 @@
     <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827869415283</t>
+    <t xml:space="preserve">8.66827964782715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318538665771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,25 +221,25 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282726287842</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966693878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924751281738</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30112,7 +30112,7 @@
     </row>
     <row r="1112">
       <c r="A1112" s="1" t="n">
-        <v>45988.6578587963</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B1112" t="n">
         <v>10463</v>
@@ -30133,6 +30133,32 @@
         <v>288</v>
       </c>
       <c r="H1112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="1" t="n">
+        <v>45989.6843981482</v>
+      </c>
+      <c r="B1113" t="n">
+        <v>348</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1113" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1113" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035499572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827964782715</t>
+    <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318538665771</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5631799697876</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157768249512</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844045639038</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353490829468</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282745361328</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966693878174</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773309707642</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
     <t xml:space="preserve">11.6635065078735</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924751281738</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30138,7 +30138,7 @@
     </row>
     <row r="1113">
       <c r="A1113" s="1" t="n">
-        <v>45989.6843981482</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B1113" t="n">
         <v>348</v>
@@ -30159,6 +30159,32 @@
         <v>289</v>
       </c>
       <c r="H1113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="1" t="n">
+        <v>45992.6910300926</v>
+      </c>
+      <c r="B1114" t="n">
+        <v>492</v>
+      </c>
+      <c r="C1114" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="G1114" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1114" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035499572754</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422306060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860805511475</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81743049621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.9490327835083</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252029418945</t>
+    <t xml:space="preserve">9.78252124786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.91412448883057</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018606185913</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353490829468</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773319244385</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -30164,7 +30164,7 @@
     </row>
     <row r="1114">
       <c r="A1114" s="1" t="n">
-        <v>45992.6910300926</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B1114" t="n">
         <v>492</v>
@@ -30185,6 +30185,32 @@
         <v>291</v>
       </c>
       <c r="H1114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="1" t="n">
+        <v>45993.6910185185</v>
+      </c>
+      <c r="B1115" t="n">
+        <v>30172</v>
+      </c>
+      <c r="C1115" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="G1115" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1115" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422306060791</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81743049621582</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.9490327835083</t>
@@ -107,43 +107,43 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384346008301</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252124786377</t>
+    <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
     <t xml:space="preserve">9.91412448883057</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025737762451</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931571960449</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
@@ -185,40 +185,40 @@
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353490829468</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -227,31 +227,31 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282745361328</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.3089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773319244385</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
     <t xml:space="preserve">12.7113990783691</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
     <t xml:space="preserve">12.2102327346802</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -30190,7 +30190,7 @@
     </row>
     <row r="1115">
       <c r="A1115" s="1" t="n">
-        <v>45993.6910185185</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B1115" t="n">
         <v>30172</v>
@@ -30211,6 +30211,32 @@
         <v>291</v>
       </c>
       <c r="H1115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="1" t="n">
+        <v>45994.6818865741</v>
+      </c>
+      <c r="B1116" t="n">
+        <v>1077</v>
+      </c>
+      <c r="C1116" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1116" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1116" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544734954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997444152832</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638931274414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931571960449</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089332580566</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.396671295166</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30216,7 +30216,7 @@
     </row>
     <row r="1116">
       <c r="A1116" s="1" t="n">
-        <v>45994.6818865741</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B1116" t="n">
         <v>1077</v>
@@ -30237,6 +30237,32 @@
         <v>289</v>
       </c>
       <c r="H1116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="1" t="n">
+        <v>45995.6912384259</v>
+      </c>
+      <c r="B1117" t="n">
+        <v>179</v>
+      </c>
+      <c r="C1117" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1117" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1117" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544734954834</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384155273438</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638931274414</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -164,31 +164,31 @@
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476110458374</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282726287842</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30242,7 +30242,7 @@
     </row>
     <row r="1117">
       <c r="A1117" s="1" t="n">
-        <v>45995.6912384259</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B1117" t="n">
         <v>179</v>
@@ -30263,6 +30263,32 @@
         <v>289</v>
       </c>
       <c r="H1117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="1" t="n">
+        <v>45996.5408333333</v>
+      </c>
+      <c r="B1118" t="n">
+        <v>54565</v>
+      </c>
+      <c r="C1118" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1118" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1118" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582439422607</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252029418945</t>
+    <t xml:space="preserve">9.78252124786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895948410034</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931476593018</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282726287842</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.1773300170898</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30268,7 +30268,7 @@
     </row>
     <row r="1118">
       <c r="A1118" s="1" t="n">
-        <v>45996.5408333333</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B1118" t="n">
         <v>54565</v>
@@ -30289,6 +30289,32 @@
         <v>289</v>
       </c>
       <c r="H1118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="1" t="n">
+        <v>45999.6824537037</v>
+      </c>
+      <c r="B1119" t="n">
+        <v>1052</v>
+      </c>
+      <c r="C1119" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1119" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1119" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -95,25 +95,25 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -131,49 +131,49 @@
     <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252124786377</t>
+    <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931476593018</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,28 +305,28 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30294,7 +30294,7 @@
     </row>
     <row r="1119">
       <c r="A1119" s="1" t="n">
-        <v>45999.6824537037</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B1119" t="n">
         <v>1052</v>
@@ -30315,6 +30315,32 @@
         <v>290</v>
       </c>
       <c r="H1119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="1" t="n">
+        <v>46000.6758912037</v>
+      </c>
+      <c r="B1120" t="n">
+        <v>17382</v>
+      </c>
+      <c r="C1120" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1120" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1120" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035308837891</t>
   </si>
   <si>
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81743049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450408935547</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5631799697876</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252029418945</t>
+    <t xml:space="preserve">9.78252124786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.91412353515625</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844045639038</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792152404785</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301578521729</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
     <t xml:space="preserve">12.7113990783691</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
     <t xml:space="preserve">12.2102327346802</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -30320,7 +30320,7 @@
     </row>
     <row r="1120">
       <c r="A1120" s="1" t="n">
-        <v>46000.6758912037</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B1120" t="n">
         <v>17382</v>
@@ -30341,6 +30341,32 @@
         <v>290</v>
       </c>
       <c r="H1120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="1" t="n">
+        <v>46001.6911342593</v>
+      </c>
+      <c r="B1121" t="n">
+        <v>443</v>
+      </c>
+      <c r="C1121" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1121" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1121" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035308837891</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.55422210693359</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81743049621582</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -131,43 +131,43 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252124786377</t>
+    <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
     <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -206,22 +206,22 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301578521729</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924751281738</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30346,7 +30346,7 @@
     </row>
     <row r="1121">
       <c r="A1121" s="1" t="n">
-        <v>46001.6911342593</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B1121" t="n">
         <v>443</v>
@@ -30367,6 +30367,32 @@
         <v>290</v>
       </c>
       <c r="H1121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="1" t="n">
+        <v>46002.6842476852</v>
+      </c>
+      <c r="B1122" t="n">
+        <v>293</v>
+      </c>
+      <c r="C1122" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1122" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1122" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,31 +50,31 @@
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582439422607</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,13 +86,13 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516376495361</t>
@@ -101,25 +101,25 @@
     <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -149,28 +149,28 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025737762451</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,49 +221,49 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282726287842</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924751281738</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30372,7 +30372,7 @@
     </row>
     <row r="1122">
       <c r="A1122" s="1" t="n">
-        <v>46002.6842476852</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B1122" t="n">
         <v>293</v>
@@ -30393,6 +30393,32 @@
         <v>290</v>
       </c>
       <c r="H1122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="1" t="n">
+        <v>46003.6911574074</v>
+      </c>
+      <c r="B1123" t="n">
+        <v>257</v>
+      </c>
+      <c r="C1123" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1123" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1123" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544734954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582439422607</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384155273438</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638931274414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -164,31 +164,31 @@
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282726287842</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30398,7 +30398,7 @@
     </row>
     <row r="1123">
       <c r="A1123" s="1" t="n">
-        <v>46003.6911574074</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B1123" t="n">
         <v>257</v>
@@ -30419,6 +30419,32 @@
         <v>289</v>
       </c>
       <c r="H1123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="1" t="n">
+        <v>46006.6829861111</v>
+      </c>
+      <c r="B1124" t="n">
+        <v>9659</v>
+      </c>
+      <c r="C1124" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1124" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1124" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -53,43 +53,43 @@
     <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544734954834</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969436645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478862762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
@@ -101,19 +101,19 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.7386531829834</t>
@@ -149,25 +149,25 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638931274414</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476110458374</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966693878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445806503296</t>
@@ -30424,7 +30424,7 @@
     </row>
     <row r="1124">
       <c r="A1124" s="1" t="n">
-        <v>46006.6829861111</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B1124" t="n">
         <v>9659</v>
@@ -30445,6 +30445,32 @@
         <v>290</v>
       </c>
       <c r="H1124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="1" t="n">
+        <v>46007.6848263889</v>
+      </c>
+      <c r="B1125" t="n">
+        <v>3036</v>
+      </c>
+      <c r="C1125" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1125" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1125" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969436645508</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478862762451</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -86,58 +86,58 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
     <t xml:space="preserve">9.7386531829834</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895948410034</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931571960449</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.3089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966693878174</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30450,7 +30450,7 @@
     </row>
     <row r="1125">
       <c r="A1125" s="1" t="n">
-        <v>46007.6848263889</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B1125" t="n">
         <v>3036</v>
@@ -30471,6 +30471,32 @@
         <v>290</v>
       </c>
       <c r="H1125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="1" t="n">
+        <v>46008.6866435185</v>
+      </c>
+      <c r="B1126" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C1126" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1126" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -98,55 +98,55 @@
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -173,55 +173,55 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931571960449</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089332580566</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
     <t xml:space="preserve">12.7113990783691</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2102327346802</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -30476,7 +30476,7 @@
     </row>
     <row r="1126">
       <c r="A1126" s="1" t="n">
-        <v>46008.6866435185</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B1126" t="n">
         <v>1125</v>
@@ -30497,6 +30497,32 @@
         <v>289</v>
       </c>
       <c r="H1126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="1" t="n">
+        <v>46009.6856712963</v>
+      </c>
+      <c r="B1127" t="n">
+        <v>3633</v>
+      </c>
+      <c r="C1127" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1127" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1127" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5631799697876</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018577575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -173,46 +173,46 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844045639038</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740249633789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30502,7 +30502,7 @@
     </row>
     <row r="1127">
       <c r="A1127" s="1" t="n">
-        <v>46009.6856712963</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B1127" t="n">
         <v>3633</v>
@@ -30523,6 +30523,32 @@
         <v>289</v>
       </c>
       <c r="H1127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="1" t="n">
+        <v>46010.691099537</v>
+      </c>
+      <c r="B1128" t="n">
+        <v>1059</v>
+      </c>
+      <c r="C1128" t="n">
+        <v>36.4000015258789</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1128" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1128" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091609954834</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895957946777</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018577575684</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546875</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740249633789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -30528,7 +30528,7 @@
     </row>
     <row r="1128">
       <c r="A1128" s="1" t="n">
-        <v>46010.691099537</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B1128" t="n">
         <v>1059</v>
@@ -30549,6 +30549,32 @@
         <v>289</v>
       </c>
       <c r="H1128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="1" t="n">
+        <v>46013.6311111111</v>
+      </c>
+      <c r="B1129" t="n">
+        <v>2107</v>
+      </c>
+      <c r="C1129" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="G1129" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1129" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035499572754</t>
+    <t xml:space="preserve">8.51035308837891</t>
   </si>
   <si>
     <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.81743049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516471862793</t>
@@ -101,52 +101,52 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252029418945</t>
+    <t xml:space="preserve">9.78252124786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740249633789</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301578521729</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30554,7 +30554,7 @@
     </row>
     <row r="1129">
       <c r="A1129" s="1" t="n">
-        <v>46013.6311111111</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B1129" t="n">
         <v>2107</v>
@@ -30575,6 +30575,32 @@
         <v>291</v>
       </c>
       <c r="H1129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="1" t="n">
+        <v>46014.6910185185</v>
+      </c>
+      <c r="B1130" t="n">
+        <v>134</v>
+      </c>
+      <c r="C1130" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1130" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1130" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035308837891</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
     <t xml:space="preserve">8.70337295532227</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81743049621582</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516471862793</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
@@ -113,49 +113,49 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252124786377</t>
+    <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38770961761475</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108184814453</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301578521729</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30580,13 +30580,13 @@
     </row>
     <row r="1130">
       <c r="A1130" s="1" t="n">
-        <v>46014.6910185185</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B1130" t="n">
         <v>134</v>
       </c>
       <c r="C1130" t="n">
-        <v>35.9000015258789</v>
+        <v>36</v>
       </c>
       <c r="D1130" t="n">
         <v>35.9000015258789</v>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860996246338</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.21223926544189</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.0018577575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740249633789</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178939819336</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985536575317</t>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,25 +50,25 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -122,31 +122,31 @@
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091609954834</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638740539551</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018577575684</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.47544574737549</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792161941528</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740249633789</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
@@ -224,55 +224,55 @@
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445806503296</t>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
@@ -95,64 +95,64 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252029418945</t>
+    <t xml:space="preserve">9.78252124786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
@@ -161,37 +161,37 @@
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157958984375</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546875</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301578521729</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179456710815</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924760818481</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30604,6 +30604,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1131">
+      <c r="A1131" s="1" t="n">
+        <v>46020.6862731482</v>
+      </c>
+      <c r="B1131" t="n">
+        <v>1336</v>
+      </c>
+      <c r="C1131" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1131" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1131" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81743049621582</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.9490327835083</t>
@@ -107,40 +107,40 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384346008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252124786377</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.7476119995117</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353490829468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301578521729</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
     <t xml:space="preserve">10.9669513702393</t>
@@ -224,31 +224,31 @@
     <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282745361328</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773319244385</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445816040039</t>
@@ -30606,7 +30606,7 @@
     </row>
     <row r="1131">
       <c r="A1131" s="1" t="n">
-        <v>46020.6862731482</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B1131" t="n">
         <v>1336</v>
@@ -30627,6 +30627,32 @@
         <v>289</v>
       </c>
       <c r="H1131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="1" t="n">
+        <v>46021.6909722222</v>
+      </c>
+      <c r="B1132" t="n">
+        <v>7831</v>
+      </c>
+      <c r="C1132" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1132" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1132" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422306060791</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860805511475</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81743049621582</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.9490327835083</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384346008301</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252124786377</t>
+    <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
     <t xml:space="preserve">9.91412448883057</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018606185913</t>
   </si>
   <si>
     <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353490829468</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773319244385</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -30632,7 +30632,7 @@
     </row>
     <row r="1132">
       <c r="A1132" s="1" t="n">
-        <v>46021.6909722222</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B1132" t="n">
         <v>7831</v>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035499572754</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.58931636810303</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -158,55 +158,55 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018606185913</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025737762451</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353490829468</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282745361328</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3445816040039</t>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -53,22 +53,22 @@
     <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073108673096</t>
+    <t xml:space="preserve">8.65073013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638835906982</t>
+    <t xml:space="preserve">9.82638740539551</t>
   </si>
   <si>
     <t xml:space="preserve">10.0895957946777</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018577575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931381225586</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -197,22 +197,22 @@
     <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740249633789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178939819336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914810180664</t>
@@ -230,34 +230,34 @@
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090654373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -266,25 +266,25 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924760818481</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079010009766</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30656,6 +30656,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1133">
+      <c r="A1133" s="1" t="n">
+        <v>46024.6913078704</v>
+      </c>
+      <c r="B1133" t="n">
+        <v>11746</v>
+      </c>
+      <c r="C1133" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1133" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1133" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65073013305664</t>
+    <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676891326904</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091609954834</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
     <t xml:space="preserve">9.6070499420166</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82638740539551</t>
+    <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018577575684</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
@@ -173,46 +173,46 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
     <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740249633789</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178939819336</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090654373169</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8001880645752</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712184906006</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30658,7 +30658,7 @@
     </row>
     <row r="1133">
       <c r="A1133" s="1" t="n">
-        <v>46024.6913078704</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B1133" t="n">
         <v>11746</v>
@@ -30679,6 +30679,32 @@
         <v>289</v>
       </c>
       <c r="H1133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="1" t="n">
+        <v>46027.6484027778</v>
+      </c>
+      <c r="B1134" t="n">
+        <v>2091</v>
+      </c>
+      <c r="C1134" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1134" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1134" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -62,22 +62,22 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582439422607</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -86,67 +86,67 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94903182983398</t>
+    <t xml:space="preserve">8.9490327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5631799697876</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844045639038</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230823516846</t>
+    <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424217224121</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282735824585</t>
+    <t xml:space="preserve">10.5282726287842</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3966703414917</t>
+    <t xml:space="preserve">10.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
     <t xml:space="preserve">12.7113990783691</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
     <t xml:space="preserve">12.2102327346802</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -30684,7 +30684,7 @@
     </row>
     <row r="1134">
       <c r="A1134" s="1" t="n">
-        <v>46027.6484027778</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B1134" t="n">
         <v>2091</v>
@@ -30705,6 +30705,32 @@
         <v>289</v>
       </c>
       <c r="H1134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="1" t="n">
+        <v>46028.6873611111</v>
+      </c>
+      <c r="B1135" t="n">
+        <v>593</v>
+      </c>
+      <c r="C1135" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G1135" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1135" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422306060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860805511475</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582439422607</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.7647876739502</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81743049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.9490327835083</t>
@@ -107,43 +107,43 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384346008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0806360244751</t>
+    <t xml:space="preserve">9.08063697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252029418945</t>
+    <t xml:space="preserve">9.78252124786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.91412448883057</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025737762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.4754467010498</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546865463257</t>
+    <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353490829468</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862897872925</t>
@@ -227,28 +227,28 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282726287842</t>
+    <t xml:space="preserve">10.5282745361328</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396671295166</t>
+    <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773319244385</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.0985546112061</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
     <t xml:space="preserve">12.7113990783691</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2102327346802</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
@@ -30710,10 +30710,10 @@
     </row>
     <row r="1135">
       <c r="A1135" s="1" t="n">
-        <v>46028.6873611111</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B1135" t="n">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="C1135" t="n">
         <v>36.0999984741211</v>
@@ -30725,10 +30725,10 @@
         <v>36</v>
       </c>
       <c r="F1135" t="n">
-        <v>36.0999984741211</v>
+        <v>36</v>
       </c>
       <c r="G1135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422306060791</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337390899658</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582630157471</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478862762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81743049621582</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9490327835083</t>
+    <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.99290084838867</t>
@@ -107,43 +107,43 @@
     <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21224021911621</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384346008301</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08063697814941</t>
+    <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
     <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252124786377</t>
+    <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
     <t xml:space="preserve">9.91412448883057</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025737762451</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.7476110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">11.0546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108194351196</t>
+    <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353490829468</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669523239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5282745361328</t>
+    <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
     <t xml:space="preserve">10.3089351654053</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773319244385</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357032775879</t>
+    <t xml:space="preserve">11.4357023239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835968017578</t>
+    <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,28 +305,28 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534618377686</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345378875732</t>
+    <t xml:space="preserve">10.9345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611738204956</t>
+    <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700531005859</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30734,6 +30734,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1136">
+      <c r="A1136" s="1" t="n">
+        <v>46029.3333333333</v>
+      </c>
+      <c r="B1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1136" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1136" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1136" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860805511475</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195823669434</t>
+    <t xml:space="preserve">8.64195728302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356052398682</t>
+    <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478862762451</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21223831176758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997444152832</t>
+    <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450313568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73846626281738</t>
+    <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.60704898834229</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412544250488</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478511810303</t>
+    <t xml:space="preserve">9.69478416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931381225586</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844064712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037448883057</t>
+    <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476110458374</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353481292725</t>
+    <t xml:space="preserve">10.8353471755981</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669523239136</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914800643921</t>
+    <t xml:space="preserve">10.7914810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598777770996</t>
+    <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179456710815</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279903411865</t>
+    <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924760818481</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079000473022</t>
+    <t xml:space="preserve">11.2079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167793273926</t>
+    <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
@@ -30760,6 +30760,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1137">
+      <c r="A1137" s="1" t="n">
+        <v>46030.3333333333</v>
+      </c>
+      <c r="B1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1137" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1137" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1137" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337295532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.68582534790039</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">8.77356147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478672027588</t>
+    <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827869415283</t>
+    <t xml:space="preserve">8.66827964782715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.89639091491699</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516376495361</t>
+    <t xml:space="preserve">8.90516471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676700592041</t>
+    <t xml:space="preserve">9.03676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223831176758</t>
+    <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384250640869</t>
+    <t xml:space="preserve">9.34384155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.12450313568115</t>
@@ -131,64 +131,64 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318092346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412544250488</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.045726776123</t>
+    <t xml:space="preserve">10.0457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001859664917</t>
+    <t xml:space="preserve">10.0018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69478416442871</t>
+    <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844064712524</t>
+    <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8353471755981</t>
+    <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740268707275</t>
+    <t xml:space="preserve">11.2740259170532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178930282593</t>
+    <t xml:space="preserve">11.3178949356079</t>
   </si>
   <si>
     <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669504165649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424236297607</t>
+    <t xml:space="preserve">11.1424226760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7914810180664</t>
+    <t xml:space="preserve">10.7914800643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
     <t xml:space="preserve">10.308934211731</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268239974976</t>
+    <t xml:space="preserve">11.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812641143799</t>
+    <t xml:space="preserve">11.4812631607056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">12.0279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534599304199</t>
+    <t xml:space="preserve">11.2534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2079010009766</t>
+    <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9345369338989</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256586074829</t>
+    <t xml:space="preserve">11.0256576538086</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3422498703003</t>
+    <t xml:space="preserve">10.342248916626</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035404205322</t>
+    <t xml:space="preserve">8.51035308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860996246338</t>
+    <t xml:space="preserve">8.55860900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544830322266</t>
+    <t xml:space="preserve">8.54544925689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64195728302002</t>
+    <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969341278076</t>
+    <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.77356147766113</t>
@@ -80,19 +80,19 @@
     <t xml:space="preserve">8.7647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66827964782715</t>
+    <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
     <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8174295425415</t>
+    <t xml:space="preserve">8.81743049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129760742188</t>
+    <t xml:space="preserve">8.86129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516471862793</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99289989471436</t>
+    <t xml:space="preserve">8.99290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">9.03676795959473</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">9.29997539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34384155273438</t>
+    <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610637664795</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837120056152</t>
+    <t xml:space="preserve">9.16837024688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450313568115</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -131,34 +131,34 @@
     <t xml:space="preserve">8.7384672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318092346191</t>
+    <t xml:space="preserve">9.56318187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6070499420166</t>
+    <t xml:space="preserve">9.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73865413665771</t>
+    <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252029418945</t>
+    <t xml:space="preserve">9.78252124786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895948410034</t>
+    <t xml:space="preserve">10.0895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799160003662</t>
+    <t xml:space="preserve">9.95799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0457277297974</t>
+    <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.0018587112427</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157768249512</t>
+    <t xml:space="preserve">9.43157863616943</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931476593018</t>
+    <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38771057128906</t>
+    <t xml:space="preserve">9.38770961761475</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">10.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.747612953186</t>
+    <t xml:space="preserve">10.7476119995117</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2740259170532</t>
+    <t xml:space="preserve">11.2740268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3178949356079</t>
+    <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301588058472</t>
+    <t xml:space="preserve">11.2301578521729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669504165649</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308934211731</t>
+    <t xml:space="preserve">10.3089351654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6598768234253</t>
+    <t xml:space="preserve">10.659875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">11.3901424407959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5268230438232</t>
+    <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001880645752</t>
+    <t xml:space="preserve">11.8001871109009</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4812631607056</t>
+    <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635065078735</t>
+    <t xml:space="preserve">11.6635055541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6179447174072</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658382415771</t>
+    <t xml:space="preserve">12.6658372879028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0279893875122</t>
+    <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
     <t xml:space="preserve">12.3924751281738</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">11.1167783737183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800977706909</t>
+    <t xml:space="preserve">10.9800968170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.6611728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256576538086</t>
+    <t xml:space="preserve">11.0256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1623392105103</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522945404053</t>
+    <t xml:space="preserve">10.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712184906006</t>
+    <t xml:space="preserve">11.0712175369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">10.5700521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342248916626</t>
+    <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035308837891</t>
+    <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422210693359</t>
+    <t xml:space="preserve">8.55422115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55860900878906</t>
+    <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931636810303</t>
+    <t xml:space="preserve">8.58931541442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54544925689697</t>
+    <t xml:space="preserve">8.54544830322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337295532227</t>
+    <t xml:space="preserve">8.70337200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582534790039</t>
+    <t xml:space="preserve">8.68582630157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77356147766113</t>
+    <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7647876739502</t>
+    <t xml:space="preserve">8.76478862762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6331844329834</t>
+    <t xml:space="preserve">8.63318347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639186859131</t>
+    <t xml:space="preserve">8.89639091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81743049621582</t>
+    <t xml:space="preserve">8.81742858886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86129665374756</t>
+    <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.90516471862793</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">9.21223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29997539520264</t>
+    <t xml:space="preserve">9.29997444152832</t>
   </si>
   <si>
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610733032227</t>
+    <t xml:space="preserve">9.25610828399658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16837024688721</t>
+    <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450408935547</t>
+    <t xml:space="preserve">9.12450218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7384672164917</t>
+    <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091800689697</t>
+    <t xml:space="preserve">9.65091705322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.56318187713623</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">9.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78252124786377</t>
+    <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412353515625</t>
+    <t xml:space="preserve">9.91412448883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">10.045726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0018587112427</t>
+    <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8702564239502</t>
+    <t xml:space="preserve">9.87025547027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43157863616943</t>
@@ -173,22 +173,22 @@
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4754467010498</t>
+    <t xml:space="preserve">9.47544574737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.51931381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38770961761475</t>
+    <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7037439346313</t>
+    <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476119995117</t>
+    <t xml:space="preserve">10.7476110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.9230833053589</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">11.0108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792152404785</t>
+    <t xml:space="preserve">10.8792161941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862897872925</t>
+    <t xml:space="preserve">11.1862907409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301578521729</t>
+    <t xml:space="preserve">11.2301597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669513702393</t>
+    <t xml:space="preserve">10.9669523239136</t>
   </si>
   <si>
     <t xml:space="preserve">11.1424226760864</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405374526978</t>
+    <t xml:space="preserve">10.4405364990234</t>
   </si>
   <si>
     <t xml:space="preserve">10.3089351654053</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773309707642</t>
+    <t xml:space="preserve">10.1773300170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721406936646</t>
+    <t xml:space="preserve">10.5721416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659875869751</t>
+    <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985546112061</t>
+    <t xml:space="preserve">11.0985536575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990207672119</t>
+    <t xml:space="preserve">11.2990217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090673446655</t>
+    <t xml:space="preserve">11.7090663909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723848342896</t>
+    <t xml:space="preserve">11.5723838806152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4357023239136</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.5268239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8001871109009</t>
+    <t xml:space="preserve">11.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">11.4812641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6635055541992</t>
+    <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179447174072</t>
+    <t xml:space="preserve">11.6179456710815</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">12.4835958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113990783691</t>
+    <t xml:space="preserve">12.7113981246948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6658372879028</t>
+    <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102327346802</t>
+    <t xml:space="preserve">12.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924751281738</t>
+    <t xml:space="preserve">12.3924760818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368696212769</t>
+    <t xml:space="preserve">11.9368686676025</t>
   </si>
   <si>
     <t xml:space="preserve">11.2534608840942</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.8889760971069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1167783737183</t>
+    <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
     <t xml:space="preserve">10.9800968170166</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067346572876</t>
+    <t xml:space="preserve">10.7067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">10.7978553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.752293586731</t>
+    <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.0712175369263</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700521469116</t>
+    <t xml:space="preserve">10.5700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.478931427002</t>
+    <t xml:space="preserve">10.4789304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445816040039</t>
+    <t xml:space="preserve">11.3445806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153017044067</t>
+    <t xml:space="preserve">12.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099100112915</t>
+    <t xml:space="preserve">12.1099109649658</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2518224716187</t>
+    <t xml:space="preserve">12.251823425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883441925049</t>
+    <t xml:space="preserve">12.4883451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356492996216</t>
+    <t xml:space="preserve">12.5356483459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817352294922</t>
+    <t xml:space="preserve">13.4817361831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248668670654</t>
+    <t xml:space="preserve">12.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721700668335</t>
+    <t xml:space="preserve">12.7721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0493879318237</t>
+    <t xml:space="preserve">14.049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182579040527</t>
+    <t xml:space="preserve">13.7182569503784</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966920852661</t>
+    <t xml:space="preserve">14.0966911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.954779624939</t>
+    <t xml:space="preserve">13.9547786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670952796936</t>
+    <t xml:space="preserve">13.6709537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344320297241</t>
+    <t xml:space="preserve">13.4344310760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697345733643</t>
+    <t xml:space="preserve">14.5697355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7116479873657</t>
+    <t xml:space="preserve">14.71164894104</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643447875977</t>
+    <t xml:space="preserve">14.6643438339233</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751272201538</t>
+    <t xml:space="preserve">14.4751262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3332138061523</t>
+    <t xml:space="preserve">14.333212852478</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535614013672</t>
+    <t xml:space="preserve">14.8535604476929</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104307174683</t>
+    <t xml:space="preserve">15.6104316711426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876495361328</t>
+    <t xml:space="preserve">16.8876476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013862609863</t>
+    <t xml:space="preserve">18.401388168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606910705566</t>
+    <t xml:space="preserve">17.3606929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146060943604</t>
+    <t xml:space="preserve">16.4146041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714744567871</t>
+    <t xml:space="preserve">17.1714725494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283447265625</t>
+    <t xml:space="preserve">17.9283428192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732515335083</t>
+    <t xml:space="preserve">18.7325172424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4893856048584</t>
+    <t xml:space="preserve">19.489387512207</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786041259766</t>
+    <t xml:space="preserve">19.6786022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8139095306396</t>
+    <t xml:space="preserve">20.813907623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>

--- a/data/ALA.MI.xlsx
+++ b/data/ALA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">ALA.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.51035404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55422115325928</t>
+    <t xml:space="preserve">8.55422210693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.55860805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58931541442871</t>
+    <t xml:space="preserve">8.58931636810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54544830322266</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">8.65073108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70337200164795</t>
+    <t xml:space="preserve">8.70337390899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68582630157471</t>
+    <t xml:space="preserve">8.68582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.64195823669434</t>
@@ -77,37 +77,37 @@
     <t xml:space="preserve">8.77356052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478862762451</t>
+    <t xml:space="preserve">8.76478672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.66827869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63318347930908</t>
+    <t xml:space="preserve">8.6331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89639091491699</t>
+    <t xml:space="preserve">8.89639186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81742858886719</t>
+    <t xml:space="preserve">8.8174295425415</t>
   </si>
   <si>
     <t xml:space="preserve">8.86129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90516471862793</t>
+    <t xml:space="preserve">8.90516376495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.94903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99290084838867</t>
+    <t xml:space="preserve">8.99289989471436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03676795959473</t>
+    <t xml:space="preserve">9.03676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21223926544189</t>
+    <t xml:space="preserve">9.21224021911621</t>
   </si>
   <si>
     <t xml:space="preserve">9.29997444152832</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.34384250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25610828399658</t>
+    <t xml:space="preserve">9.25610733032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.16837120056152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12450218200684</t>
+    <t xml:space="preserve">9.12450408935547</t>
   </si>
   <si>
     <t xml:space="preserve">9.0806360244751</t>
@@ -131,31 +131,31 @@
     <t xml:space="preserve">8.73846626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65091705322266</t>
+    <t xml:space="preserve">9.65091800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56318187713623</t>
+    <t xml:space="preserve">9.5631799697876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60704898834229</t>
+    <t xml:space="preserve">9.6070499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7386531829834</t>
+    <t xml:space="preserve">9.73865413665771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78252029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91412448883057</t>
+    <t xml:space="preserve">9.91412353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.82638835906982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0895957946777</t>
+    <t xml:space="preserve">10.0895948410034</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95799255371094</t>
+    <t xml:space="preserve">9.95799160003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.045726776123</t>
@@ -164,49 +164,49 @@
     <t xml:space="preserve">10.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87025547027588</t>
+    <t xml:space="preserve">9.8702564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43157863616943</t>
+    <t xml:space="preserve">9.43157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.69478511810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47544574737549</t>
+    <t xml:space="preserve">9.4754467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51931381225586</t>
+    <t xml:space="preserve">9.51931476593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.38771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844055175781</t>
+    <t xml:space="preserve">10.4844045639038</t>
   </si>
   <si>
     <t xml:space="preserve">10.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7476110458374</t>
+    <t xml:space="preserve">10.747612953186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9230833053589</t>
+    <t xml:space="preserve">10.9230823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0546875</t>
+    <t xml:space="preserve">11.0546865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0108184814453</t>
+    <t xml:space="preserve">11.0108194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8792161941528</t>
+    <t xml:space="preserve">10.8792152404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.8353481292725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862907409668</t>
+    <t xml:space="preserve">11.1862897872925</t>
   </si>
   <si>
     <t xml:space="preserve">11.2740268707275</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">11.3178930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2301597595215</t>
+    <t xml:space="preserve">11.2301588058472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9669523239136</t>
+    <t xml:space="preserve">10.9669513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1424226760864</t>
+    <t xml:space="preserve">11.1424217224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.7914800643921</t>
@@ -230,43 +230,43 @@
     <t xml:space="preserve">10.5282735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405364990234</t>
+    <t xml:space="preserve">10.4405374526978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3089351654053</t>
+    <t xml:space="preserve">10.308934211731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1773300170898</t>
+    <t xml:space="preserve">10.1773309707642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5721416473389</t>
+    <t xml:space="preserve">10.5721406936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6598777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0985536575317</t>
+    <t xml:space="preserve">11.0985546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2990217208862</t>
+    <t xml:space="preserve">11.2990207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090663909912</t>
+    <t xml:space="preserve">11.7090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723838806152</t>
+    <t xml:space="preserve">11.5723848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4357023239136</t>
+    <t xml:space="preserve">11.4357032775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3901424407959</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">11.6635065078735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6179456710815</t>
+    <t xml:space="preserve">11.6179447174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.8457479476929</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">11.8913087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4835958480835</t>
+    <t xml:space="preserve">12.4835968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7113981246948</t>
+    <t xml:space="preserve">12.7113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.7569599151611</t>
@@ -305,28 +305,28 @@
     <t xml:space="preserve">12.6658382415771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2102317810059</t>
+    <t xml:space="preserve">12.2102327346802</t>
   </si>
   <si>
     <t xml:space="preserve">12.0279903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3924760818481</t>
+    <t xml:space="preserve">12.3924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9824295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9368686676025</t>
+    <t xml:space="preserve">11.9368696212769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2534608840942</t>
+    <t xml:space="preserve">11.2534618377686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9345369338989</t>
+    <t xml:space="preserve">10.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.8889760971069</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">11.1167793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9800968170166</t>
+    <t xml:space="preserve">10.9800977706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6611728668213</t>
+    <t xml:space="preserve">10.6611738204956</t>
   </si>
   <si>
     <t xml:space="preserve">11.0256586074829</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.1623392105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7067337036133</t>
+    <t xml:space="preserve">10.7067346572876</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434152603149</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">10.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0712175369263</t>
+    <t xml:space="preserve">11.0712184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700511932373</t>
+    <t xml:space="preserve">10.5700531005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.3422498703003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789304733276</t>
+    <t xml:space="preserve">10.478931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3445806503296</t>
+    <t xml:space="preserve">11.3445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0153007507324</t>
+    <t xml:space="preserve">12.0153017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1099109649658</t>
+    <t xml:space="preserve">12.1099100112915</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045183181763</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">12.2991275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.251823425293</t>
+    <t xml:space="preserve">12.2518224716187</t>
   </si>
   <si>
     <t xml:space="preserve">12.4410400390625</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">12.582953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4883451461792</t>
+    <t xml:space="preserve">12.4883441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5356483459473</t>
+    <t xml:space="preserve">12.5356492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.6775617599487</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">13.339822769165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4817361831665</t>
+    <t xml:space="preserve">13.4817352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248659133911</t>
+    <t xml:space="preserve">12.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">12.8667802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7721710205078</t>
+    <t xml:space="preserve">12.7721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.2925186157227</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">13.5290403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.049388885498</t>
+    <t xml:space="preserve">14.0493879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7182569503784</t>
+    <t xml:space="preserve">13.7182579040527</t>
   </si>
   <si>
     <t xml:space="preserve">14.3805179595947</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">14.2386054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0966911315918</t>
+    <t xml:space="preserve">14.0966920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547786712646</t>
+    <t xml:space="preserve">13.954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6709537506104</t>
+    <t xml:space="preserve">13.670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.8128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344310760498</t>
+    <t xml:space="preserve">13.4344320297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.7655620574951</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">15.0900831222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5697355270386</t>
+    <t xml:space="preserve">14.5697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.71164894104</t>
+    <t xml:space="preserve">14.7116479873657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9481706619263</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">15.042778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6643438339233</t>
+    <t xml:space="preserve">14.6643447875977</t>
   </si>
   <si>
     <t xml:space="preserve">14.7589530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4751262664795</t>
+    <t xml:space="preserve">14.4751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.333212852478</t>
+    <t xml:space="preserve">14.3332138061523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1373872756958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">14.9954748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8535604476929</t>
+    <t xml:space="preserve">14.8535614013672</t>
   </si>
   <si>
     <t xml:space="preserve">15.326605796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6104316711426</t>
+    <t xml:space="preserve">15.6104307174683</t>
   </si>
   <si>
     <t xml:space="preserve">15.8942556381226</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">17.407995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8876476287842</t>
+    <t xml:space="preserve">16.8876495361328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6511268615723</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">18.5433006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.401388168335</t>
+    <t xml:space="preserve">18.4013862609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.9349517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3606929779053</t>
+    <t xml:space="preserve">17.3606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4146041870117</t>
+    <t xml:space="preserve">16.4146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1714725494385</t>
+    <t xml:space="preserve">17.1714744567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8403434753418</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.2594738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9283428192139</t>
+    <t xml:space="preserve">17.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.0229511260986</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">18.5906047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7325172424316</t>
+    <t xml:space="preserve">18.732515335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.8810386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.489387512207</t>
+    <t xml:space="preserve">19.4893856048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6786022186279</t>
+    <t xml:space="preserve">19.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3001689910889</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">20.0570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.813907623291</t>
+    <t xml:space="preserve">20.8139095306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.3815612792969</t>
